--- a/diseases/d109/1995-1999.xlsx
+++ b/diseases/d109/1995-1999.xlsx
@@ -1403,7 +1403,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8513,7 +8513,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9303,7 +9303,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -10093,7 +10093,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10883,7 +10883,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11673,7 +11673,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12463,7 +12463,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13253,7 +13253,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -14043,7 +14043,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14833,7 +14833,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15623,7 +15623,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -16413,7 +16413,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -17203,7 +17203,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -17993,7 +17993,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18783,7 +18783,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19573,7 +19573,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN102" t="b">
@@ -21615,7 +21615,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -22636,7 +22636,7 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN112" t="b">
@@ -23657,7 +23657,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -24678,7 +24678,7 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN122" t="b">
@@ -25699,7 +25699,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -26720,7 +26720,7 @@
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN132" t="b">
@@ -27741,7 +27741,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -28762,7 +28762,7 @@
       </c>
       <c r="AM142" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN142" t="b">
@@ -29783,7 +29783,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -30804,7 +30804,7 @@
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN152" t="b">
@@ -31825,7 +31825,7 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -32846,7 +32846,7 @@
       </c>
       <c r="AM162" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN162" t="b">
@@ -33867,7 +33867,7 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -34888,7 +34888,7 @@
       </c>
       <c r="AM172" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN172" t="b">
@@ -35909,7 +35909,7 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN177" t="b">
@@ -36930,7 +36930,7 @@
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN182" t="b">
@@ -37951,7 +37951,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -38972,7 +38972,7 @@
       </c>
       <c r="AM192" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN192" t="b">
@@ -39993,7 +39993,7 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN197" t="b">
@@ -41014,7 +41014,7 @@
       </c>
       <c r="AM202" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN202" t="b">
@@ -42035,7 +42035,7 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -43056,7 +43056,7 @@
       </c>
       <c r="AM212" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN212" t="b">
@@ -44077,7 +44077,7 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN217" t="b">
@@ -45098,7 +45098,7 @@
       </c>
       <c r="AM222" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN222" t="b">
@@ -46119,7 +46119,7 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -47140,7 +47140,7 @@
       </c>
       <c r="AM232" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN232" t="b">
@@ -48161,7 +48161,7 @@
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN237" t="b">
@@ -49182,7 +49182,7 @@
       </c>
       <c r="AM242" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN242" t="b">
@@ -50203,7 +50203,7 @@
       </c>
       <c r="AM247" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN247" t="b">
@@ -51224,7 +51224,7 @@
       </c>
       <c r="AM252" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN252" t="b">
@@ -52245,7 +52245,7 @@
       </c>
       <c r="AM257" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN257" t="b">
@@ -53266,7 +53266,7 @@
       </c>
       <c r="AM262" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN262" t="b">
@@ -54287,7 +54287,7 @@
       </c>
       <c r="AM267" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN267" t="b">
@@ -55308,7 +55308,7 @@
       </c>
       <c r="AM272" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN272" t="b">
@@ -56329,7 +56329,7 @@
       </c>
       <c r="AM277" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN277" t="b">

--- a/diseases/d109/1995-1999.xlsx
+++ b/diseases/d109/1995-1999.xlsx
@@ -1403,7 +1403,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8513,7 +8513,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9303,7 +9303,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -10093,7 +10093,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10883,7 +10883,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11673,7 +11673,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12463,7 +12463,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -13253,7 +13253,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -14043,7 +14043,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14833,7 +14833,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15623,7 +15623,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -16413,7 +16413,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -17203,7 +17203,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -17993,7 +17993,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18783,7 +18783,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19573,7 +19573,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN102" t="b">
@@ -21615,7 +21615,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -22636,7 +22636,7 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN112" t="b">
@@ -23657,7 +23657,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -24678,7 +24678,7 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN122" t="b">
@@ -25699,7 +25699,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -26720,7 +26720,7 @@
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN132" t="b">
@@ -27741,7 +27741,7 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -28762,7 +28762,7 @@
       </c>
       <c r="AM142" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN142" t="b">
@@ -29783,7 +29783,7 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -30804,7 +30804,7 @@
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN152" t="b">
@@ -31825,7 +31825,7 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -32846,7 +32846,7 @@
       </c>
       <c r="AM162" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN162" t="b">
@@ -33867,7 +33867,7 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -34888,7 +34888,7 @@
       </c>
       <c r="AM172" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN172" t="b">
@@ -35909,7 +35909,7 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN177" t="b">
@@ -36930,7 +36930,7 @@
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN182" t="b">
@@ -37951,7 +37951,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -38972,7 +38972,7 @@
       </c>
       <c r="AM192" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN192" t="b">
@@ -39993,7 +39993,7 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN197" t="b">
@@ -41014,7 +41014,7 @@
       </c>
       <c r="AM202" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN202" t="b">
@@ -42035,7 +42035,7 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN207" t="b">
@@ -43056,7 +43056,7 @@
       </c>
       <c r="AM212" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN212" t="b">
@@ -44077,7 +44077,7 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN217" t="b">
@@ -45098,7 +45098,7 @@
       </c>
       <c r="AM222" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN222" t="b">
@@ -46119,7 +46119,7 @@
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -47140,7 +47140,7 @@
       </c>
       <c r="AM232" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN232" t="b">
@@ -48161,7 +48161,7 @@
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN237" t="b">
@@ -49182,7 +49182,7 @@
       </c>
       <c r="AM242" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN242" t="b">
@@ -50203,7 +50203,7 @@
       </c>
       <c r="AM247" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN247" t="b">
@@ -51224,7 +51224,7 @@
       </c>
       <c r="AM252" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN252" t="b">
@@ -52245,7 +52245,7 @@
       </c>
       <c r="AM257" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN257" t="b">
@@ -53266,7 +53266,7 @@
       </c>
       <c r="AM262" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN262" t="b">
@@ -54287,7 +54287,7 @@
       </c>
       <c r="AM267" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN267" t="b">
@@ -55308,7 +55308,7 @@
       </c>
       <c r="AM272" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN272" t="b">
@@ -56329,7 +56329,7 @@
       </c>
       <c r="AM277" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN277" t="b">
